--- a/files/港岛-半山区西部-天御第1期.xlsx
+++ b/files/港岛-半山区西部-天御第1期.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5930,1414 +5797,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天御第1期 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>106 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>94 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>PH52E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>52&amp;53&amp;55/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>PH52E | 11200呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>- | 4655呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (3房)
-$35,496万
-$75,363/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>49/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr"/>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="16" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr"/>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="16" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr"/>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="16" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr"/>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="16" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr"/>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="16" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>- | 4710呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr"/>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>- | 4596呎 (3房)
-$26,898万
-$58,526/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr"/>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>A | 2269呎 (4+房)
-$11,288万
-$49,749/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>B | 2281呎 (4+房)
-$11,928万
-$52,293/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr"/>
-      <c r="G22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr"/>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>A | 2269呎 (4+房)
-$10,924万
-$48,144/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>B | 2281呎 (4+房)
-$14,183万
-$62,180/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr"/>
-      <c r="G23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr"/>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>A | 2269呎 (4+房)
-$10,428万
-$45,960/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>B | 2281呎 (4+房)
-$11,222万
-$49,198/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr"/>
-      <c r="F24" s="16" t="inlineStr"/>
-      <c r="G24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr"/>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>A | 2269呎 (4+房)
-$10,820万
-$47,686/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>B | 2281呎 (4+房)
-$10,214万
-$44,778/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr"/>
-      <c r="F25" s="16" t="inlineStr"/>
-      <c r="G25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr"/>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>A | 2269呎 (4+房)
-$9,800万
-$43,191/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>B | 2281呎 (4+房)
-$10,337万
-$45,318/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr"/>
-      <c r="F26" s="16" t="inlineStr"/>
-      <c r="G26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr"/>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr"/>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr"/>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr"/>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr"/>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr"/>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr"/>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr"/>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr"/>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr"/>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr"/>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr"/>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr"/>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr"/>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr"/>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr"/>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr"/>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr"/>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr"/>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr"/>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr"/>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr"/>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr"/>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr"/>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr"/>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr"/>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr"/>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr"/>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr"/>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr"/>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr"/>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr"/>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr"/>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr"/>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr"/>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>A | 1424呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>B | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>D | 1404呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr"/>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr"/>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>A | 1395呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>B | 834呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t>C | 834呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>D | 1376呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山区西部-天御第1期.xlsx
+++ b/files/港岛-半山区西部-天御第1期.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +136,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +217,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -5797,4 +5967,1414 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>PH52E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>52&amp;53&amp;55</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>PH52E | 11200呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>- | 4655呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (3房)
+$35496万
+$75,363/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>- | 4710呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>- | 4596呎 (3房)
+$26898万
+$58,526/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr"/>
+      <c r="G20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>A | 2269呎 (4+房)
+$11288万
+$49,749/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>B | 2281呎 (4+房)
+$11928万
+$52,293/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>A | 2269呎 (4+房)
+$10924万
+$48,144/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>B | 2281呎 (4+房)
+$14183万
+$62,180/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr"/>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>A | 2269呎 (4+房)
+$10428万
+$45,960/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>B | 2281呎 (4+房)
+$11222万
+$49,198/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr"/>
+      <c r="F23" s="20" t="inlineStr"/>
+      <c r="G23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>A | 2269呎 (4+房)
+$10820万
+$47,686/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>B | 2281呎 (4+房)
+$10214万
+$44,778/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>A | 2269呎 (4+房)
+$9800万
+$43,191/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>B | 2281呎 (4+房)
+$10337万
+$45,318/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr"/>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr"/>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr"/>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr"/>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr"/>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr"/>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr"/>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr"/>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr"/>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr"/>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr"/>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr"/>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr"/>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr"/>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr"/>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>A | 1424呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>B | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>D | 1404呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr"/>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr"/>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>A | 1395呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>B | 834呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>C | 834呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>D | 1376呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山区西部-天御第1期.xlsx
+++ b/files/港岛-半山区西部-天御第1期.xlsx
@@ -644,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区西部-天御第1期.xlsx
+++ b/files/港岛-半山区西部-天御第1期.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -704,6 +708,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -754,6 +778,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -804,6 +848,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -850,6 +914,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -900,6 +984,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -950,6 +1054,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1000,6 +1124,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1050,6 +1194,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1100,6 +1264,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1150,6 +1334,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1200,6 +1404,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1250,6 +1474,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1300,6 +1544,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1350,6 +1614,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1400,6 +1684,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1450,6 +1754,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1496,6 +1820,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1542,6 +1886,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1588,6 +1952,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1634,6 +2018,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1680,6 +2084,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1726,6 +2150,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1772,6 +2216,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1818,6 +2282,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1864,6 +2348,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1910,6 +2414,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1956,6 +2480,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2006,6 +2550,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2056,6 +2620,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2106,6 +2690,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2156,6 +2760,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2206,6 +2830,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2256,6 +2900,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2306,6 +2970,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2356,6 +3040,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2406,6 +3110,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2456,6 +3180,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2506,6 +3250,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2556,6 +3320,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2606,6 +3390,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2656,6 +3460,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2706,6 +3530,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2756,6 +3600,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2806,6 +3670,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2856,6 +3740,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2906,6 +3810,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2956,6 +3880,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3006,6 +3950,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3056,6 +4020,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3106,6 +4090,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3156,6 +4160,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3206,6 +4230,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3256,6 +4300,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3306,6 +4370,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3356,6 +4440,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3406,6 +4510,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3456,6 +4580,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3506,6 +4650,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3556,6 +4720,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3606,6 +4790,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3656,6 +4860,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3706,6 +4930,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3756,6 +5000,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3806,6 +5070,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3856,6 +5140,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3906,6 +5210,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3956,6 +5280,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4006,6 +5350,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4056,6 +5420,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4106,6 +5490,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4156,6 +5560,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4206,6 +5630,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4256,6 +5700,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4306,6 +5770,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4356,6 +5840,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4406,6 +5910,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4456,6 +5980,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4506,6 +6050,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4556,6 +6120,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4606,6 +6190,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4656,6 +6260,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4706,6 +6330,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4756,6 +6400,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4806,6 +6470,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4856,6 +6540,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4906,6 +6610,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4956,6 +6680,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5006,6 +6750,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5056,6 +6820,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5106,6 +6890,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5156,6 +6960,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5206,6 +7030,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5256,6 +7100,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5306,6 +7170,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5356,6 +7240,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5406,6 +7310,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5456,6 +7380,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5506,6 +7450,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5556,6 +7520,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5606,6 +7590,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5656,6 +7660,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5706,6 +7730,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5756,6 +7800,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5806,6 +7870,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5856,6 +7940,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5906,6 +8010,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5956,13 +8080,33 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6146,7 +8290,7 @@
           <t>- | 4710呎 (3房)
 $35496万
 $75,363/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -6406,7 +8550,7 @@
           <t>- | 4596呎 (3房)
 $26898万
 $58,526/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -6427,7 +8571,7 @@
           <t>A | 2269呎 (4+房)
 $11288万
 $49,749/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -6435,7 +8579,7 @@
           <t>B | 2281呎 (4+房)
 $11928万
 $52,293/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr"/>
@@ -6454,7 +8598,7 @@
           <t>A | 2269呎 (4+房)
 $10924万
 $48,144/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -6462,7 +8606,7 @@
           <t>B | 2281呎 (4+房)
 $14183万
 $62,180/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr"/>
@@ -6481,7 +8625,7 @@
           <t>A | 2269呎 (4+房)
 $10428万
 $45,960/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -6489,7 +8633,7 @@
           <t>B | 2281呎 (4+房)
 $11222万
 $49,198/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr"/>
@@ -6508,7 +8652,7 @@
           <t>A | 2269呎 (4+房)
 $10820万
 $47,686/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -6516,7 +8660,7 @@
           <t>B | 2281呎 (4+房)
 $10214万
 $44,778/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
@@ -6535,7 +8679,7 @@
           <t>A | 2269呎 (4+房)
 $9800万
 $43,191/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -6543,7 +8687,7 @@
           <t>B | 2281呎 (4+房)
 $10337万
 $45,318/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr"/>

--- a/files/港岛-半山区西部-天御第1期.xlsx
+++ b/files/港岛-半山区西部-天御第1期.xlsx
@@ -8290,7 +8290,7 @@
           <t>- | 4710呎 (3房)
 $35496万
 $75,363/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -8550,7 +8550,7 @@
           <t>- | 4596呎 (3房)
 $26898万
 $58,526/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -8571,7 +8571,7 @@
           <t>A | 2269呎 (4+房)
 $11288万
 $49,749/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -8579,7 +8579,7 @@
           <t>B | 2281呎 (4+房)
 $11928万
 $52,293/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr"/>
@@ -8598,7 +8598,7 @@
           <t>A | 2269呎 (4+房)
 $10924万
 $48,144/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -8606,7 +8606,7 @@
           <t>B | 2281呎 (4+房)
 $14183万
 $62,180/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr"/>
@@ -8625,7 +8625,7 @@
           <t>A | 2269呎 (4+房)
 $10428万
 $45,960/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -8633,7 +8633,7 @@
           <t>B | 2281呎 (4+房)
 $11222万
 $49,198/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr"/>
@@ -8652,7 +8652,7 @@
           <t>A | 2269呎 (4+房)
 $10820万
 $47,686/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -8660,7 +8660,7 @@
           <t>B | 2281呎 (4+房)
 $10214万
 $44,778/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
@@ -8679,7 +8679,7 @@
           <t>A | 2269呎 (4+房)
 $9800万
 $43,191/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -8687,7 +8687,7 @@
           <t>B | 2281呎 (4+房)
 $10337万
 $45,318/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr"/>

--- a/files/港岛-半山区西部-天御第1期.xlsx
+++ b/files/港岛-半山区西部-天御第1期.xlsx
@@ -8290,7 +8290,7 @@
           <t>- | 4710呎 (3房)
 $35496万
 $75,363/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -8550,7 +8550,7 @@
           <t>- | 4596呎 (3房)
 $26898万
 $58,526/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -8571,7 +8571,7 @@
           <t>A | 2269呎 (4+房)
 $11288万
 $49,749/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -8579,7 +8579,7 @@
           <t>B | 2281呎 (4+房)
 $11928万
 $52,293/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr"/>
@@ -8598,7 +8598,7 @@
           <t>A | 2269呎 (4+房)
 $10924万
 $48,144/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -8606,7 +8606,7 @@
           <t>B | 2281呎 (4+房)
 $14183万
 $62,180/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr"/>
@@ -8625,7 +8625,7 @@
           <t>A | 2269呎 (4+房)
 $10428万
 $45,960/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -8633,7 +8633,7 @@
           <t>B | 2281呎 (4+房)
 $11222万
 $49,198/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr"/>
@@ -8652,7 +8652,7 @@
           <t>A | 2269呎 (4+房)
 $10820万
 $47,686/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -8660,7 +8660,7 @@
           <t>B | 2281呎 (4+房)
 $10214万
 $44,778/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
@@ -8679,7 +8679,7 @@
           <t>A | 2269呎 (4+房)
 $9800万
 $43,191/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -8687,7 +8687,7 @@
           <t>B | 2281呎 (4+房)
 $10337万
 $45,318/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr"/>
